--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91506</v>
+        <v>91580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127098897</v>
       </c>
       <c r="B3" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127098859</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098900</v>
+        <v>127098856</v>
       </c>
       <c r="B5" t="n">
-        <v>78386</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625535</v>
+        <v>625842</v>
       </c>
       <c r="R5" t="n">
-        <v>7310214</v>
+        <v>7310297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098856</v>
+        <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>79598</v>
+        <v>78417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625842</v>
+        <v>625535</v>
       </c>
       <c r="R6" t="n">
-        <v>7310297</v>
+        <v>7310214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>127098895</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127098863</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098892</v>
+        <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>97245</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625825</v>
+        <v>626159</v>
       </c>
       <c r="R9" t="n">
-        <v>7310234</v>
+        <v>7309665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098862</v>
+        <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>79598</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626159</v>
+        <v>625825</v>
       </c>
       <c r="R10" t="n">
-        <v>7309665</v>
+        <v>7310234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>127098899</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>127098901</v>
       </c>
       <c r="B12" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>79598</v>
+        <v>78678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>127098861</v>
       </c>
       <c r="B15" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127098897</v>
       </c>
       <c r="B3" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127098859</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127098856</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127098895</v>
       </c>
       <c r="B7" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127098863</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>127098899</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>127098901</v>
       </c>
       <c r="B12" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B13" t="n">
-        <v>78678</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R13" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R14" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>127098861</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098862</v>
+        <v>127098892</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>97326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626159</v>
+        <v>625825</v>
       </c>
       <c r="R9" t="n">
-        <v>7309665</v>
+        <v>7310234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098892</v>
+        <v>127098862</v>
       </c>
       <c r="B10" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625825</v>
+        <v>626159</v>
       </c>
       <c r="R10" t="n">
-        <v>7310234</v>
+        <v>7309665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098892</v>
+        <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625825</v>
+        <v>626159</v>
       </c>
       <c r="R9" t="n">
-        <v>7310234</v>
+        <v>7309665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098862</v>
+        <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>97326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626159</v>
+        <v>625825</v>
       </c>
       <c r="R10" t="n">
-        <v>7309665</v>
+        <v>7310234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R13" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R14" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098859</v>
+        <v>127098900</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626105</v>
+        <v>625535</v>
       </c>
       <c r="R4" t="n">
-        <v>7309826</v>
+        <v>7310214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098856</v>
+        <v>127098859</v>
       </c>
       <c r="B5" t="n">
         <v>79632</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625842</v>
+        <v>626105</v>
       </c>
       <c r="R5" t="n">
-        <v>7310297</v>
+        <v>7309826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098900</v>
+        <v>127098856</v>
       </c>
       <c r="B6" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625535</v>
+        <v>625842</v>
       </c>
       <c r="R6" t="n">
-        <v>7310214</v>
+        <v>7310297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098900</v>
+        <v>127098859</v>
       </c>
       <c r="B4" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625535</v>
+        <v>626105</v>
       </c>
       <c r="R4" t="n">
-        <v>7310214</v>
+        <v>7309826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098859</v>
+        <v>127098856</v>
       </c>
       <c r="B5" t="n">
         <v>79632</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626105</v>
+        <v>625842</v>
       </c>
       <c r="R5" t="n">
-        <v>7309826</v>
+        <v>7310297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098856</v>
+        <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625842</v>
+        <v>625535</v>
       </c>
       <c r="R6" t="n">
-        <v>7310297</v>
+        <v>7310214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098862</v>
+        <v>127098892</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626159</v>
+        <v>625825</v>
       </c>
       <c r="R9" t="n">
-        <v>7309665</v>
+        <v>7310234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098892</v>
+        <v>127098862</v>
       </c>
       <c r="B10" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625825</v>
+        <v>626159</v>
       </c>
       <c r="R10" t="n">
-        <v>7310234</v>
+        <v>7309665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127098897</v>
       </c>
       <c r="B3" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098859</v>
+        <v>127098856</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626105</v>
+        <v>625842</v>
       </c>
       <c r="R4" t="n">
-        <v>7309826</v>
+        <v>7310297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098856</v>
+        <v>127098859</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625842</v>
+        <v>626105</v>
       </c>
       <c r="R5" t="n">
-        <v>7310297</v>
+        <v>7309826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127098895</v>
       </c>
       <c r="B7" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127098863</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098892</v>
+        <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>97327</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625825</v>
+        <v>626159</v>
       </c>
       <c r="R9" t="n">
-        <v>7310234</v>
+        <v>7309665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098862</v>
+        <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>97331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626159</v>
+        <v>625825</v>
       </c>
       <c r="R10" t="n">
-        <v>7309665</v>
+        <v>7310234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>127098899</v>
       </c>
       <c r="B11" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>127098901</v>
       </c>
       <c r="B12" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>127098861</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098856</v>
+        <v>127098859</v>
       </c>
       <c r="B4" t="n">
         <v>79636</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625842</v>
+        <v>626105</v>
       </c>
       <c r="R4" t="n">
-        <v>7310297</v>
+        <v>7309826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098859</v>
+        <v>127098856</v>
       </c>
       <c r="B5" t="n">
         <v>79636</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626105</v>
+        <v>625842</v>
       </c>
       <c r="R5" t="n">
-        <v>7309826</v>
+        <v>7310297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R13" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R14" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91591</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127098897</v>
       </c>
       <c r="B3" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127098859</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>127098856</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127098895</v>
       </c>
       <c r="B7" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127098863</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>127098899</v>
       </c>
       <c r="B11" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>127098901</v>
       </c>
       <c r="B12" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R13" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R14" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>127098861</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91580</v>
+        <v>91610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127098897</v>
       </c>
       <c r="B3" t="n">
-        <v>78678</v>
+        <v>78696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098859</v>
+        <v>127098856</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626105</v>
+        <v>625842</v>
       </c>
       <c r="R4" t="n">
-        <v>7309826</v>
+        <v>7310297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098856</v>
+        <v>127098859</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625842</v>
+        <v>626105</v>
       </c>
       <c r="R5" t="n">
-        <v>7310297</v>
+        <v>7309826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>127098900</v>
       </c>
       <c r="B6" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>127098895</v>
       </c>
       <c r="B7" t="n">
-        <v>78678</v>
+        <v>78696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>127098863</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127098862</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>127098892</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>97350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>127098899</v>
       </c>
       <c r="B11" t="n">
-        <v>78678</v>
+        <v>78696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>127098901</v>
       </c>
       <c r="B12" t="n">
-        <v>78417</v>
+        <v>78435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098896</v>
+        <v>127098858</v>
       </c>
       <c r="B13" t="n">
-        <v>78678</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625562</v>
+        <v>626047</v>
       </c>
       <c r="R13" t="n">
-        <v>7310301</v>
+        <v>7309948</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098858</v>
+        <v>127098896</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626047</v>
+        <v>625562</v>
       </c>
       <c r="R14" t="n">
-        <v>7309948</v>
+        <v>7310301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>127098861</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127098894</v>
       </c>
       <c r="B2" t="n">
-        <v>91610</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098897</v>
+        <v>127098895</v>
       </c>
       <c r="B3" t="n">
-        <v>78696</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625698</v>
+        <v>625527</v>
       </c>
       <c r="R3" t="n">
-        <v>7309928</v>
+        <v>7310213</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098856</v>
+        <v>127098896</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625842</v>
+        <v>625562</v>
       </c>
       <c r="R4" t="n">
-        <v>7310297</v>
+        <v>7310301</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098859</v>
+        <v>127098897</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626105</v>
+        <v>625698</v>
       </c>
       <c r="R5" t="n">
-        <v>7309826</v>
+        <v>7309928</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098900</v>
+        <v>127098899</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625535</v>
+        <v>625917</v>
       </c>
       <c r="R6" t="n">
-        <v>7310214</v>
+        <v>7309647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127098895</v>
+        <v>127098900</v>
       </c>
       <c r="B7" t="n">
-        <v>78696</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625527</v>
+        <v>625535</v>
       </c>
       <c r="R7" t="n">
-        <v>7310213</v>
+        <v>7310214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127098863</v>
+        <v>127098901</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626085</v>
+        <v>625972</v>
       </c>
       <c r="R8" t="n">
-        <v>7309617</v>
+        <v>7309679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098862</v>
+        <v>127098856</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626159</v>
+        <v>625842</v>
       </c>
       <c r="R9" t="n">
-        <v>7309665</v>
+        <v>7310297</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098892</v>
+        <v>127098857</v>
       </c>
       <c r="B10" t="n">
-        <v>97350</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625825</v>
+        <v>625827</v>
       </c>
       <c r="R10" t="n">
-        <v>7310234</v>
+        <v>7310045</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098899</v>
+        <v>127098858</v>
       </c>
       <c r="B11" t="n">
-        <v>78696</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625917</v>
+        <v>626047</v>
       </c>
       <c r="R11" t="n">
-        <v>7309647</v>
+        <v>7309948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127098901</v>
+        <v>127098859</v>
       </c>
       <c r="B12" t="n">
-        <v>78435</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625972</v>
+        <v>626105</v>
       </c>
       <c r="R12" t="n">
-        <v>7309679</v>
+        <v>7309826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098858</v>
+        <v>127098861</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626047</v>
+        <v>626123</v>
       </c>
       <c r="R13" t="n">
-        <v>7309948</v>
+        <v>7309763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098896</v>
+        <v>127098862</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625562</v>
+        <v>626159</v>
       </c>
       <c r="R14" t="n">
-        <v>7310301</v>
+        <v>7309665</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127098861</v>
+        <v>127098863</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626123</v>
+        <v>626085</v>
       </c>
       <c r="R15" t="n">
-        <v>7309763</v>
+        <v>7309617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127098857</v>
+        <v>134352940</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>57391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,34 +2184,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>102961</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Mullholm, Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625827</v>
+        <v>625788</v>
       </c>
       <c r="R16" t="n">
-        <v>7310045</v>
+        <v>7309754</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>05:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>05:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,6 +2277,113 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127098892</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>625825</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7310234</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098895</v>
+        <v>135333147</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>92220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625527</v>
+        <v>625668</v>
       </c>
       <c r="R3" t="n">
-        <v>7310213</v>
+        <v>7309535</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,19 +877,23 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098896</v>
+        <v>127098895</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625562</v>
+        <v>625527</v>
       </c>
       <c r="R4" t="n">
-        <v>7310301</v>
+        <v>7310213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098897</v>
+        <v>127098896</v>
       </c>
       <c r="B5" t="n">
         <v>78993</v>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625698</v>
+        <v>625562</v>
       </c>
       <c r="R5" t="n">
-        <v>7309928</v>
+        <v>7310301</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098899</v>
+        <v>127098897</v>
       </c>
       <c r="B6" t="n">
         <v>78993</v>
@@ -1138,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625917</v>
+        <v>625698</v>
       </c>
       <c r="R6" t="n">
-        <v>7309647</v>
+        <v>7309928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127098900</v>
+        <v>127098899</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625535</v>
+        <v>625917</v>
       </c>
       <c r="R7" t="n">
-        <v>7310214</v>
+        <v>7309647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127098901</v>
+        <v>135333486</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1356,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625972</v>
+        <v>625696</v>
       </c>
       <c r="R8" t="n">
-        <v>7309679</v>
+        <v>7309881</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,22 +1386,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,22 +1416,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098856</v>
+        <v>135330525</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625842</v>
+        <v>625735</v>
       </c>
       <c r="R9" t="n">
-        <v>7310297</v>
+        <v>7310220</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,22 +1497,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1527,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098857</v>
+        <v>135333487</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>92027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1578,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625827</v>
+        <v>625699</v>
       </c>
       <c r="R10" t="n">
-        <v>7310045</v>
+        <v>7309882</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,22 +1608,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,22 +1638,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098858</v>
+        <v>135330526</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>93271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1689,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626047</v>
+        <v>625805</v>
       </c>
       <c r="R11" t="n">
-        <v>7309948</v>
+        <v>7310208</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,22 +1719,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjol</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,22 +1754,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127098859</v>
+        <v>127098900</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626105</v>
+        <v>625535</v>
       </c>
       <c r="R12" t="n">
-        <v>7309826</v>
+        <v>7310214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098861</v>
+        <v>127098901</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626123</v>
+        <v>625972</v>
       </c>
       <c r="R13" t="n">
-        <v>7309763</v>
+        <v>7309679</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098862</v>
+        <v>135333471</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626159</v>
+        <v>625571</v>
       </c>
       <c r="R14" t="n">
-        <v>7309665</v>
+        <v>7310000</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2024,22 +2049,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,19 +2079,23 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127098863</v>
+        <v>127098856</v>
       </c>
       <c r="B15" t="n">
         <v>79946</v>
@@ -2101,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626085</v>
+        <v>625842</v>
       </c>
       <c r="R15" t="n">
-        <v>7309617</v>
+        <v>7310297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2165,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2175,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2202,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134352940</v>
+        <v>127098857</v>
       </c>
       <c r="B16" t="n">
-        <v>57391</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,34 +2213,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102961</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mullholm, Mullholm, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625788</v>
+        <v>625827</v>
       </c>
       <c r="R16" t="n">
-        <v>7309754</v>
+        <v>7310045</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,22 +2267,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2309,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127098892</v>
+        <v>127098858</v>
       </c>
       <c r="B17" t="n">
-        <v>97989</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625825</v>
+        <v>626047</v>
       </c>
       <c r="R17" t="n">
-        <v>7310234</v>
+        <v>7309948</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,6 +2413,3231 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127098859</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626105</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7309826</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127098861</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626123</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7309763</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127098862</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626159</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7309665</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127098863</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7309617</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135330521</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625537</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7310019</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135330522</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>625565</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7310032</v>
+      </c>
+      <c r="S23" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135333145</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>625804</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7309692</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135333148</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>625824</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7309606</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135330204</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626118</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7309934</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Brottsplatsen, förmodligen av en duvhök</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135330205</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7309903</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fågelbo av okänd art, förmodligen dovhök, inga kännetecken på besättning.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135330528</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57921</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>625738</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7310074</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjädrar</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135333492</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>625656</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7309880</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134352940</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mullholm, Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>625788</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7309754</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135333482</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>625723</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7309686</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135330535</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>625610</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7310059</v>
+      </c>
+      <c r="S32" t="n">
+        <v>23</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Läten</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135333468</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>625526</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7310020</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135333475</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>625621</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7309943</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135333479</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625785</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7309854</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135330206</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7309862</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135333473</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>625566</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7310008</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127098892</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>625825</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7310234</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135330523</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>625545</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135333144</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>625851</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7309768</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135330524</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>625573</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135330527</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>625803</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7310164</v>
+      </c>
+      <c r="S42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135333140</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>625522</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7310019</v>
+      </c>
+      <c r="S43" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135333142</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>625850</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7309817</v>
+      </c>
+      <c r="S44" t="n">
+        <v>19</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135333149</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>625697</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7309876</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135333480</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>625807</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7309723</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135333486</v>
+        <v>135331250</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625696</v>
+        <v>625548</v>
       </c>
       <c r="R8" t="n">
-        <v>7309881</v>
+        <v>7309987</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,12 +1416,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135330525</v>
+        <v>135331255</v>
       </c>
       <c r="B9" t="n">
-        <v>92027</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625735</v>
+        <v>625702</v>
       </c>
       <c r="R9" t="n">
-        <v>7310220</v>
+        <v>7310040</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,12 +1527,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135333487</v>
+        <v>135331256</v>
       </c>
       <c r="B10" t="n">
-        <v>92027</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625699</v>
+        <v>625716</v>
       </c>
       <c r="R10" t="n">
-        <v>7309882</v>
+        <v>7310035</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,12 +1638,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135330526</v>
+        <v>135331257</v>
       </c>
       <c r="B11" t="n">
-        <v>93271</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625805</v>
+        <v>625697</v>
       </c>
       <c r="R11" t="n">
-        <v>7310208</v>
+        <v>7310027</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,12 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fjol</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,12 +1749,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1770,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127098900</v>
+        <v>135333486</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625535</v>
+        <v>625696</v>
       </c>
       <c r="R12" t="n">
-        <v>7310214</v>
+        <v>7309881</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,22 +1830,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,22 +1860,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098901</v>
+        <v>135331253</v>
       </c>
       <c r="B13" t="n">
-        <v>78730</v>
+        <v>81355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,13 +1911,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625972</v>
+        <v>625587</v>
       </c>
       <c r="R13" t="n">
-        <v>7309679</v>
+        <v>7310173</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,22 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,22 +1971,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135333471</v>
+        <v>135333296</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>81355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,21 +1998,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2019,13 +2022,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625571</v>
+        <v>626068</v>
       </c>
       <c r="R14" t="n">
-        <v>7310000</v>
+        <v>7309771</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,12 +2082,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2095,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127098856</v>
+        <v>135330525</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,21 +2109,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2130,13 +2133,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625842</v>
+        <v>625735</v>
       </c>
       <c r="R15" t="n">
-        <v>7310297</v>
+        <v>7310220</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2160,22 +2163,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,22 +2193,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127098857</v>
+        <v>135333295</v>
       </c>
       <c r="B16" t="n">
-        <v>79946</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,21 +2220,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2237,13 +2244,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625827</v>
+        <v>626062</v>
       </c>
       <c r="R16" t="n">
-        <v>7310045</v>
+        <v>7309776</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2267,22 +2274,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,22 +2304,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127098858</v>
+        <v>135333487</v>
       </c>
       <c r="B17" t="n">
-        <v>79946</v>
+        <v>92027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2344,13 +2355,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626047</v>
+        <v>625699</v>
       </c>
       <c r="R17" t="n">
-        <v>7309948</v>
+        <v>7309882</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,22 +2385,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,22 +2415,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127098859</v>
+        <v>135330526</v>
       </c>
       <c r="B18" t="n">
-        <v>79946</v>
+        <v>93271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,21 +2442,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,13 +2466,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626105</v>
+        <v>625805</v>
       </c>
       <c r="R18" t="n">
-        <v>7309826</v>
+        <v>7310208</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,22 +2496,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fjol</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,22 +2531,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127098861</v>
+        <v>135331258</v>
       </c>
       <c r="B19" t="n">
-        <v>79946</v>
+        <v>93271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,21 +2558,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2558,13 +2582,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626123</v>
+        <v>625711</v>
       </c>
       <c r="R19" t="n">
-        <v>7309763</v>
+        <v>7310024</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,22 +2612,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,60 +2642,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127098862</v>
+        <v>135337867</v>
       </c>
       <c r="B20" t="n">
-        <v>79946</v>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Översikt tre objekt, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626159</v>
+        <v>625593</v>
       </c>
       <c r="R20" t="n">
-        <v>7309665</v>
+        <v>7310031</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2695,22 +2723,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2725,22 +2753,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127098863</v>
+        <v>127098900</v>
       </c>
       <c r="B21" t="n">
-        <v>79946</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,21 +2780,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2772,10 +2804,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626085</v>
+        <v>625535</v>
       </c>
       <c r="R21" t="n">
-        <v>7309617</v>
+        <v>7310214</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2839,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2849,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,10 +2876,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135330521</v>
+        <v>127098901</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,21 +2887,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2879,13 +2911,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625537</v>
+        <v>625972</v>
       </c>
       <c r="R22" t="n">
-        <v>7310019</v>
+        <v>7309679</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2909,22 +2941,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2939,26 +2971,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135330522</v>
+        <v>135331251</v>
       </c>
       <c r="B23" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,21 +2994,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2990,13 +3018,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>625565</v>
+        <v>625573</v>
       </c>
       <c r="R23" t="n">
-        <v>7310032</v>
+        <v>7310131</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3025,7 +3053,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3035,7 +3063,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3050,12 +3078,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3066,10 +3094,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333145</v>
+        <v>135331252</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3077,37 +3105,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>625804</v>
+        <v>625585</v>
       </c>
       <c r="R24" t="n">
-        <v>7309692</v>
+        <v>7310155</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3136,7 +3164,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3146,7 +3174,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,12 +3189,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3177,10 +3205,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135333148</v>
+        <v>135333471</v>
       </c>
       <c r="B25" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,37 +3216,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>625824</v>
+        <v>625571</v>
       </c>
       <c r="R25" t="n">
-        <v>7309606</v>
+        <v>7310000</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3247,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3257,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,12 +3300,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3288,10 +3316,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135330204</v>
+        <v>127098856</v>
       </c>
       <c r="B26" t="n">
-        <v>57896</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,34 +3327,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>626118</v>
+        <v>625842</v>
       </c>
       <c r="R26" t="n">
-        <v>7309934</v>
+        <v>7310297</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,27 +3381,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Brottsplatsen, förmodligen av en duvhök</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,26 +3411,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135330205</v>
+        <v>127098857</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,34 +3434,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100001</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>626140</v>
+        <v>625827</v>
       </c>
       <c r="R27" t="n">
-        <v>7309903</v>
+        <v>7310045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,27 +3488,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fågelbo av okänd art, förmodligen dovhök, inga kännetecken på besättning.</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3504,48 +3518,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135330528</v>
+        <v>127098858</v>
       </c>
       <c r="B28" t="n">
-        <v>57921</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100067</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3555,13 +3565,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625738</v>
+        <v>626047</v>
       </c>
       <c r="R28" t="n">
-        <v>7310074</v>
+        <v>7309948</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3585,27 +3595,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjädrar</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3620,48 +3625,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135333492</v>
+        <v>127098859</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,13 +3672,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625656</v>
+        <v>626105</v>
       </c>
       <c r="R29" t="n">
-        <v>7309880</v>
+        <v>7309826</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3701,27 +3702,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,26 +3732,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134352940</v>
+        <v>127098861</v>
       </c>
       <c r="B30" t="n">
-        <v>57391</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3763,34 +3755,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102961</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mullholm, Mullholm, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625788</v>
+        <v>626123</v>
       </c>
       <c r="R30" t="n">
-        <v>7309754</v>
+        <v>7309763</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,22 +3809,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3859,10 +3851,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135333482</v>
+        <v>127098862</v>
       </c>
       <c r="B31" t="n">
-        <v>57391</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3870,21 +3862,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102961</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3894,13 +3886,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>625723</v>
+        <v>626159</v>
       </c>
       <c r="R31" t="n">
-        <v>7309686</v>
+        <v>7309665</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3924,22 +3916,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,26 +3946,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135330535</v>
+        <v>127098863</v>
       </c>
       <c r="B32" t="n">
-        <v>58136</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,21 +3969,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4005,13 +3993,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>625610</v>
+        <v>626085</v>
       </c>
       <c r="R32" t="n">
-        <v>7310059</v>
+        <v>7309617</v>
       </c>
       <c r="S32" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4035,27 +4023,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Läten</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,26 +4053,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135333468</v>
+        <v>135330521</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4097,21 +4076,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4121,13 +4100,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>625526</v>
+        <v>625537</v>
       </c>
       <c r="R33" t="n">
-        <v>7310020</v>
+        <v>7310019</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4156,7 +4135,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4166,7 +4145,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4181,12 +4160,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4197,10 +4176,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135333475</v>
+        <v>135330522</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4208,21 +4187,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4232,13 +4211,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>625621</v>
+        <v>625565</v>
       </c>
       <c r="R34" t="n">
-        <v>7309943</v>
+        <v>7310032</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4267,7 +4246,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4277,7 +4256,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4292,12 +4271,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4308,10 +4287,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135333479</v>
+        <v>135331249</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4319,21 +4298,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4343,10 +4322,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625785</v>
+        <v>625537</v>
       </c>
       <c r="R35" t="n">
-        <v>7309854</v>
+        <v>7310022</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4378,7 +4357,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4388,7 +4367,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4403,12 +4382,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4419,10 +4398,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135330206</v>
+        <v>135331254</v>
       </c>
       <c r="B36" t="n">
-        <v>58079</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4430,34 +4409,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626140</v>
+        <v>625736</v>
       </c>
       <c r="R36" t="n">
-        <v>7309862</v>
+        <v>7310232</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4489,7 +4468,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4499,12 +4478,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:44</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4519,12 +4493,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4535,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135333473</v>
+        <v>135333145</v>
       </c>
       <c r="B37" t="n">
-        <v>56706</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,37 +4520,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>206046</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>625566</v>
+        <v>625804</v>
       </c>
       <c r="R37" t="n">
-        <v>7310008</v>
+        <v>7309692</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4605,7 +4579,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4615,7 +4589,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4630,12 +4604,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4646,48 +4620,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127098892</v>
+        <v>135333148</v>
       </c>
       <c r="B38" t="n">
-        <v>97989</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>625825</v>
+        <v>625824</v>
       </c>
       <c r="R38" t="n">
-        <v>7310234</v>
+        <v>7309606</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4711,22 +4685,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4741,22 +4715,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135330523</v>
+        <v>135333297</v>
       </c>
       <c r="B39" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,21 +4742,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4788,13 +4766,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>625545</v>
+        <v>626120</v>
       </c>
       <c r="R39" t="n">
-        <v>7310168</v>
+        <v>7309749</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4823,7 +4801,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4833,7 +4811,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,12 +4826,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4864,10 +4842,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135333144</v>
+        <v>135333300</v>
       </c>
       <c r="B40" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4875,37 +4853,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>625851</v>
+        <v>625604</v>
       </c>
       <c r="R40" t="n">
-        <v>7309768</v>
+        <v>7309865</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4934,7 +4912,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,7 +4922,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4959,12 +4937,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4975,10 +4953,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135330524</v>
+        <v>135337870</v>
       </c>
       <c r="B41" t="n">
-        <v>79396</v>
+        <v>79992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4986,37 +4964,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>260591</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Översikt tre objekt, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>625573</v>
+        <v>626072</v>
       </c>
       <c r="R41" t="n">
-        <v>7310171</v>
+        <v>7309765</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5045,7 +5023,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5055,7 +5033,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5070,12 +5048,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5086,10 +5064,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135330527</v>
+        <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>79396</v>
+        <v>57896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5097,37 +5075,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>260591</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>625803</v>
+        <v>626118</v>
       </c>
       <c r="R42" t="n">
-        <v>7310164</v>
+        <v>7309934</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5156,7 +5134,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5166,7 +5144,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Brottsplatsen, förmodligen av en duvhök</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5181,12 +5164,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5197,10 +5180,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135333140</v>
+        <v>135330205</v>
       </c>
       <c r="B43" t="n">
-        <v>79396</v>
+        <v>57896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,37 +5191,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>260591</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>625522</v>
+        <v>626140</v>
       </c>
       <c r="R43" t="n">
-        <v>7310019</v>
+        <v>7309903</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5267,7 +5250,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5277,7 +5260,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fågelbo av okänd art, förmodligen dovhök, inga kännetecken på besättning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5292,12 +5280,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5308,48 +5296,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135333142</v>
+        <v>135333292</v>
       </c>
       <c r="B44" t="n">
-        <v>79396</v>
+        <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>260591</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>625850</v>
+        <v>625892</v>
       </c>
       <c r="R44" t="n">
-        <v>7309817</v>
+        <v>7309935</v>
       </c>
       <c r="S44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5378,7 +5371,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5388,7 +5381,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5403,12 +5396,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5419,48 +5412,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135333149</v>
+        <v>135330528</v>
       </c>
       <c r="B45" t="n">
-        <v>79396</v>
+        <v>57921</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>260591</v>
+        <v>100067</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>625697</v>
+        <v>625738</v>
       </c>
       <c r="R45" t="n">
-        <v>7309876</v>
+        <v>7310074</v>
       </c>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5489,7 +5482,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5499,7 +5492,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fjädrar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5514,12 +5512,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5530,10 +5528,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135333480</v>
+        <v>135333294</v>
       </c>
       <c r="B46" t="n">
-        <v>79396</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5541,21 +5539,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5565,13 +5563,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>625807</v>
+        <v>626079</v>
       </c>
       <c r="R46" t="n">
-        <v>7309723</v>
+        <v>7309824</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5600,7 +5598,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5610,14 +5608,19 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>barkfläk på undertryckt gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5625,15 +5628,2363 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135333492</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>625656</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7309880</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134352940</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mullholm, Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>625788</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7309754</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135333482</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>625723</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7309686</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135330535</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>625610</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310059</v>
+      </c>
+      <c r="S50" t="n">
+        <v>23</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Läten</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135333289</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>625559</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310017</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135333298</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626109</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7309638</v>
+      </c>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135333468</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>625526</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310020</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135333475</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>625621</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7309943</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135333479</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>625785</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7309854</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135330206</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7309862</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135333299</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>626054</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7309677</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135333473</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56706</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>625566</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310008</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127098892</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>625825</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7310234</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135330523</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>625545</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S60" t="n">
+        <v>11</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135333144</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>625851</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7309768</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135330524</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>625573</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135330527</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>625803</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7310164</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135333140</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>625522</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7310019</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135333142</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>625850</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7309817</v>
+      </c>
+      <c r="S65" t="n">
+        <v>19</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135333149</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>625697</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7309876</v>
+      </c>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135333480</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>625807</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7309723</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098894</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098895</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098897</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098899</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331255</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333486</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333296</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330525</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333295</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2544,6 +2629,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330526</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2655,6 +2745,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331258</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2766,6 +2861,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337867</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2873,6 +2973,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098900</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2980,6 +3085,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098901</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3091,6 +3201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331251</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331252</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3313,6 +3433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333471</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3420,6 +3545,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098856</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3527,6 +3657,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098857</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3634,6 +3769,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098858</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3741,6 +3881,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098859</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3848,6 +3993,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098861</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3955,6 +4105,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4062,6 +4217,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098863</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4173,6 +4333,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330521</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4284,6 +4449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330522</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4395,6 +4565,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331249</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4506,6 +4681,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331254</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4617,6 +4797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333145</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4728,6 +4913,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333148</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4839,6 +5029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333297</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4950,6 +5145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333300</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5061,6 +5261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337870</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5177,6 +5382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330204</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5293,6 +5503,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330205</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5409,6 +5624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333292</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5525,6 +5745,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330528</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5641,6 +5866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333294</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5757,6 +5987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333492</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5864,6 +6099,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134352940</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5975,6 +6215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333482</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6091,6 +6336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330535</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6207,6 +6457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333289</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6323,6 +6578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333298</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6434,6 +6694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333468</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6545,6 +6810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333475</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6656,6 +6926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333479</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6772,6 +7047,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330206</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6883,6 +7163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333299</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6994,6 +7279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333473</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7101,6 +7391,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098892</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7212,6 +7507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330523</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7323,6 +7623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333144</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7434,6 +7739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330524</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7545,6 +7855,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330527</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7656,6 +7971,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333140</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7767,6 +8087,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333142</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7878,6 +8203,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333149</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7989,8 +8319,81 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333480</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135333147</v>
       </c>
       <c r="B3" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135331250</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135331255</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135331256</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135331257</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135333486</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135331253</v>
       </c>
       <c r="B13" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>135333296</v>
       </c>
       <c r="B14" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>135330525</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>135333295</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135333487</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135330526</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135331258</v>
       </c>
       <c r="B19" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>135337867</v>
       </c>
       <c r="B20" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135331251</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>135331252</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>135333471</v>
       </c>
       <c r="B25" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135330521</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135330522</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135331249</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>135331254</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>135333145</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>135333148</v>
       </c>
       <c r="B38" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135333297</v>
       </c>
       <c r="B39" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>135333300</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>135337870</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>135330204</v>
       </c>
       <c r="B42" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>135330205</v>
       </c>
       <c r="B43" t="n">
-        <v>57896</v>
+        <v>57901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>135333292</v>
       </c>
       <c r="B44" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>135330528</v>
       </c>
       <c r="B45" t="n">
-        <v>57921</v>
+        <v>57926</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>135333294</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>135333492</v>
       </c>
       <c r="B47" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>135333482</v>
       </c>
       <c r="B49" t="n">
-        <v>57391</v>
+        <v>57396</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>135330535</v>
       </c>
       <c r="B50" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135333289</v>
       </c>
       <c r="B51" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>135333298</v>
       </c>
       <c r="B52" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>135333468</v>
       </c>
       <c r="B53" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135333475</v>
       </c>
       <c r="B54" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>135333479</v>
       </c>
       <c r="B55" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>135330206</v>
       </c>
       <c r="B56" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>135333299</v>
       </c>
       <c r="B57" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>135333473</v>
       </c>
       <c r="B58" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135330523</v>
       </c>
       <c r="B60" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135333144</v>
       </c>
       <c r="B61" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135330524</v>
       </c>
       <c r="B62" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>135330527</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>135333140</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>135333142</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>135333149</v>
       </c>
       <c r="B66" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>135333480</v>
       </c>
       <c r="B67" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135333147</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135331250</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135331255</v>
       </c>
       <c r="B9" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>135331256</v>
       </c>
       <c r="B10" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135331257</v>
       </c>
       <c r="B11" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135333486</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135331253</v>
       </c>
       <c r="B13" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>135333296</v>
       </c>
       <c r="B14" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>135330525</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>135333295</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135333487</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135330526</v>
       </c>
       <c r="B18" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135331258</v>
       </c>
       <c r="B19" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>135337867</v>
       </c>
       <c r="B20" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>135331251</v>
       </c>
       <c r="B23" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>135331252</v>
       </c>
       <c r="B24" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>135333471</v>
       </c>
       <c r="B25" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135330521</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>135330522</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>135331249</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>135331254</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>135333145</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>135333148</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>135333297</v>
       </c>
       <c r="B39" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>135333300</v>
       </c>
       <c r="B40" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>135337870</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>135330523</v>
       </c>
       <c r="B60" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>135333144</v>
       </c>
       <c r="B61" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>135330524</v>
       </c>
       <c r="B62" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>135330527</v>
       </c>
       <c r="B63" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>135333140</v>
       </c>
       <c r="B64" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>135333142</v>
       </c>
       <c r="B65" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>135333149</v>
       </c>
       <c r="B66" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>135333480</v>
       </c>
       <c r="B67" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,48 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127098895</v>
+        <v>135333147</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mullholm, Pi lm</t>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625527</v>
+        <v>625668</v>
       </c>
       <c r="R3" t="n">
-        <v>7310213</v>
+        <v>7309535</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +887,28 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098895</t>
+          <t>https://artportalen.se/Sighting/135333147</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127098896</v>
+        <v>127098895</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625562</v>
+        <v>625527</v>
       </c>
       <c r="R4" t="n">
-        <v>7310301</v>
+        <v>7310213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +1014,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098896</t>
+          <t>https://artportalen.se/Sighting/127098895</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127098897</v>
+        <v>127098896</v>
       </c>
       <c r="B5" t="n">
         <v>78993</v>
@@ -1051,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625698</v>
+        <v>625562</v>
       </c>
       <c r="R5" t="n">
-        <v>7309928</v>
+        <v>7310301</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1126,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098897</t>
+          <t>https://artportalen.se/Sighting/127098896</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127098899</v>
+        <v>127098897</v>
       </c>
       <c r="B6" t="n">
         <v>78993</v>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625917</v>
+        <v>625698</v>
       </c>
       <c r="R6" t="n">
-        <v>7309647</v>
+        <v>7309928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1238,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098899</t>
+          <t>https://artportalen.se/Sighting/127098897</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127098900</v>
+        <v>127098899</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625535</v>
+        <v>625917</v>
       </c>
       <c r="R7" t="n">
-        <v>7310214</v>
+        <v>7309647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1350,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098900</t>
+          <t>https://artportalen.se/Sighting/127098899</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127098901</v>
+        <v>135331250</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>79107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1367,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625972</v>
+        <v>625548</v>
       </c>
       <c r="R8" t="n">
-        <v>7309679</v>
+        <v>7309987</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1421,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1451,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098901</t>
+          <t>https://artportalen.se/Sighting/135331250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127098856</v>
+        <v>135331255</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>79107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1483,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625842</v>
+        <v>625702</v>
       </c>
       <c r="R9" t="n">
-        <v>7310297</v>
+        <v>7310040</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1537,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1567,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098856</t>
+          <t>https://artportalen.se/Sighting/135331255</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127098857</v>
+        <v>135331256</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>79107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1623,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625827</v>
+        <v>625716</v>
       </c>
       <c r="R10" t="n">
-        <v>7310045</v>
+        <v>7310035</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1653,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1683,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098857</t>
+          <t>https://artportalen.se/Sighting/135331256</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127098858</v>
+        <v>135331257</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>79107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626047</v>
+        <v>625697</v>
       </c>
       <c r="R11" t="n">
-        <v>7309948</v>
+        <v>7310027</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1769,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1799,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098858</t>
+          <t>https://artportalen.se/Sighting/135331257</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127098859</v>
+        <v>135333486</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>79107</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1855,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626105</v>
+        <v>625696</v>
       </c>
       <c r="R12" t="n">
-        <v>7309826</v>
+        <v>7309881</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1885,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,27 +1915,31 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098859</t>
+          <t>https://artportalen.se/Sighting/135333486</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127098861</v>
+        <v>135331253</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>81423</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1971,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626123</v>
+        <v>625587</v>
       </c>
       <c r="R13" t="n">
-        <v>7309763</v>
+        <v>7310173</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,22 +2001,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +2031,31 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098861</t>
+          <t>https://artportalen.se/Sighting/135331253</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127098862</v>
+        <v>135333296</v>
       </c>
       <c r="B14" t="n">
-        <v>79946</v>
+        <v>81423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2063,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2087,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626159</v>
+        <v>626068</v>
       </c>
       <c r="R14" t="n">
-        <v>7309665</v>
+        <v>7309771</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +2117,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,27 +2147,31 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098862</t>
+          <t>https://artportalen.se/Sighting/135333296</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127098863</v>
+        <v>135330525</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2203,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626085</v>
+        <v>625735</v>
       </c>
       <c r="R15" t="n">
-        <v>7309617</v>
+        <v>7310220</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,22 +2233,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,27 +2263,31 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127098863</t>
+          <t>https://artportalen.se/Sighting/135330525</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134352940</v>
+        <v>135333295</v>
       </c>
       <c r="B16" t="n">
-        <v>57391</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,37 +2295,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102961</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mullholm, Mullholm, Pi lm</t>
+          <t>Mullholm, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625788</v>
+        <v>626062</v>
       </c>
       <c r="R16" t="n">
-        <v>7309754</v>
+        <v>7309776</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2349,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,49 +2379,53 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134352940</t>
+          <t>https://artportalen.se/Sighting/135333295</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127098892</v>
+        <v>135333487</v>
       </c>
       <c r="B17" t="n">
-        <v>97989</v>
+        <v>92101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2435,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625825</v>
+        <v>625699</v>
       </c>
       <c r="R17" t="n">
-        <v>7310234</v>
+        <v>7309882</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,22 +2465,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,18 +2495,5833 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333487</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135330526</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>625805</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fjol</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330526</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135331258</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>625711</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7310024</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331258</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135337867</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Översikt tre objekt, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625593</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7310031</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337867</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127098900</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625535</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7310214</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr">
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098900</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127098901</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625972</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7309679</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098901</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135331251</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>625573</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7310131</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331251</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135331252</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>625585</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7310155</v>
+      </c>
+      <c r="S24" t="n">
+        <v>14</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331252</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135333471</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>625571</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7310000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333471</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127098856</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>625842</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7310297</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098856</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127098857</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>625827</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7310045</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098857</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127098858</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626047</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7309948</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098858</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127098859</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626105</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7309826</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098859</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127098861</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>626123</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7309763</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098861</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127098862</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626159</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7309665</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098862</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127098863</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626085</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7309617</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098863</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135330521</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>625537</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7310019</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330521</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135330522</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>625565</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7310032</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330522</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135331249</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625537</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7310022</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331249</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135331254</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>625736</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7310232</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331254</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135333145</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>625804</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7309692</v>
+      </c>
+      <c r="S37" t="n">
+        <v>12</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333145</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135333148</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>625824</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7309606</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333148</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135333297</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626120</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7309749</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333297</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135333300</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>625604</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7309865</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333300</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135337870</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Översikt tre objekt, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626072</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7309765</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337870</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135330204</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57901</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626118</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7309934</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Brottsplatsen, förmodligen av en duvhök</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330204</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135330205</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57901</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7309903</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fågelbo av okänd art, förmodligen dovhök, inga kännetecken på besättning.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330205</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135333292</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>625892</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7309935</v>
+      </c>
+      <c r="S44" t="n">
+        <v>9</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333292</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135330528</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57926</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>625738</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7310074</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fjädrar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330528</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135333294</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626079</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7309824</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>barkfläk på undertryckt gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333294</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135333492</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>625656</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7309880</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333492</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134352940</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57391</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mullholm, Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>625788</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7309754</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>05:36</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134352940</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135333482</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57396</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>625723</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7309686</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333482</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135330535</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>625610</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310059</v>
+      </c>
+      <c r="S50" t="n">
+        <v>23</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Läten</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330535</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135333289</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>625559</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310017</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333289</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135333298</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626109</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7309638</v>
+      </c>
+      <c r="S52" t="n">
+        <v>13</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333298</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135333468</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>625526</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310020</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333468</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135333475</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>625621</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7309943</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333475</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135333479</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>625785</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7309854</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333479</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135330206</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>626140</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7309862</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330206</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135333299</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>626054</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7309677</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333299</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135333473</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>625566</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310008</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333473</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127098892</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>625825</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7310234</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127098892</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135330523</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>625545</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S60" t="n">
+        <v>11</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330523</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135333144</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>625851</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7309768</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333144</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135330524</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>625573</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S62" t="n">
+        <v>8</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330524</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135330527</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>625803</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7310164</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330527</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135333140</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>625522</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7310019</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333140</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135333142</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>625850</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7309817</v>
+      </c>
+      <c r="S65" t="n">
+        <v>19</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333142</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135333149</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Mullholm+Myrås_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>625697</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7309876</v>
+      </c>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333149</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135333480</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mullholm, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>625807</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7309723</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333480</t>
         </is>
       </c>
     </row>
@@ -2488,6 +8343,56 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34430-2025 artfynd.xlsx
+++ b/artfynd/A 34430-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135333147</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>135330525</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>135333295</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135333487</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135330526</v>
       </c>
       <c r="B18" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>135331258</v>
       </c>
       <c r="B19" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>135337867</v>
       </c>
       <c r="B20" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
